--- a/bases/Wim_Pif/projects/nominee-owners-load/build/garant_format0.xlsx
+++ b/bases/Wim_Pif/projects/nominee-owners-load/build/garant_format0.xlsx
@@ -28,7 +28,7 @@
     <t>- 614007,Permskiy kray,g Perm,ul Testovaya,d 1,kv 1</t>
   </si>
   <si>
-    <t>TEST_ND_20260916081258_Ivanov Ivan Ivanovich</t>
+    <t>TEST_ND_20260916093443_Ivanov Ivan Ivanovich</t>
   </si>
   <si>
     <t>10</t>
@@ -55,7 +55,7 @@
     <t>21.05.2018</t>
   </si>
   <si>
-    <t>01_20260916081258_NRD_OLD</t>
+    <t>01_20260916093443_NRD_OLD</t>
   </si>
 </sst>
 </file>
